--- a/templates/Student_template.xlsx
+++ b/templates/Student_template.xlsx
@@ -1,17 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="7" rupBuild="4505"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23801"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Pro_Final\c_p_m_new\templates\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C4ED7A5-946A-459B-B48D-0AC1AD3F25DA}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20730" windowHeight="9075"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="124519"/>
-  <extLst xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main">
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
@@ -24,69 +30,21 @@
     <t>email</t>
   </si>
   <si>
-    <t>18IT401</t>
-  </si>
-  <si>
-    <t>smit</t>
-  </si>
-  <si>
     <t>smit@gmail.com</t>
   </si>
   <si>
-    <t>18IT402</t>
-  </si>
-  <si>
-    <t>harsh</t>
-  </si>
-  <si>
     <t>harsh@gmail.com</t>
   </si>
   <si>
-    <t>18IT403</t>
-  </si>
-  <si>
-    <t>yash</t>
-  </si>
-  <si>
-    <t>yash@gmail.com</t>
-  </si>
-  <si>
-    <t>18IT404</t>
-  </si>
-  <si>
-    <t>jeet</t>
-  </si>
-  <si>
-    <t>jeet@gmail.com</t>
-  </si>
-  <si>
-    <t>18IT405</t>
-  </si>
-  <si>
-    <t>taksh</t>
-  </si>
-  <si>
-    <t>taksh@gmail.com</t>
-  </si>
-  <si>
     <t>id</t>
   </si>
   <si>
     <t>last_name</t>
   </si>
   <si>
-    <t>ghelani</t>
-  </si>
-  <si>
     <t>patel</t>
   </si>
   <si>
-    <t>maheta</t>
-  </si>
-  <si>
-    <t>shah</t>
-  </si>
-  <si>
     <t>Username</t>
   </si>
   <si>
@@ -96,14 +54,62 @@
     <t>dept</t>
   </si>
   <si>
-    <t>IT</t>
+    <t>18ME401</t>
+  </si>
+  <si>
+    <t>Harsh</t>
+  </si>
+  <si>
+    <t>Mechanical</t>
+  </si>
+  <si>
+    <t>18ME402</t>
+  </si>
+  <si>
+    <t>18ME403</t>
+  </si>
+  <si>
+    <t>18ME404</t>
+  </si>
+  <si>
+    <t>18ME405</t>
+  </si>
+  <si>
+    <t>Tirth</t>
+  </si>
+  <si>
+    <t>Dhruvin</t>
+  </si>
+  <si>
+    <t>Mangrola</t>
+  </si>
+  <si>
+    <t>dhruvin@gmail.com</t>
+  </si>
+  <si>
+    <t>tirth@gmail.com</t>
+  </si>
+  <si>
+    <t>Smit</t>
+  </si>
+  <si>
+    <t>Dabhi</t>
+  </si>
+  <si>
+    <t>netri@gmail.com</t>
+  </si>
+  <si>
+    <t>Patel</t>
+  </si>
+  <si>
+    <t>Netry</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -115,6 +121,12 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -451,129 +463,130 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="B1" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="C1" t="s">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="D1" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="E1" t="s">
         <v>0</v>
       </c>
       <c r="F1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="B2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="B3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="B5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="E6" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F6" t="s">
         <v>11</v>
-      </c>
-      <c r="D5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="B6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F6" t="s">
-        <v>25</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="E2" r:id="rId1"/>
-    <hyperlink ref="E3" r:id="rId2"/>
-    <hyperlink ref="E4" r:id="rId3"/>
-    <hyperlink ref="E5" r:id="rId4"/>
-    <hyperlink ref="E6" r:id="rId5"/>
+    <hyperlink ref="E2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="E3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="E4" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="E5" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="E6" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
